--- a/output/pdf_financials_xlsx/MDP.xlsx
+++ b/output/pdf_financials_xlsx/MDP.xlsx
@@ -2520,7 +2520,7 @@
         <v>2.295</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.301</v>
+        <v>12.439</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>8.003</v>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">

--- a/output/pdf_financials_xlsx/MDP.xlsx
+++ b/output/pdf_financials_xlsx/MDP.xlsx
@@ -879,25 +879,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.049227</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.041469</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.039952</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0398</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.21593</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1626,25 +1626,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.998949</v>
+        <v>-4.949722</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.299294</v>
+        <v>-2.257825</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.831887</v>
+        <v>-1.791935</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.482645</v>
+        <v>-3.442845</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-6.300213</v>
+        <v>-6.084283</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-5.545</v>
+        <v>-5.325</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-31.501</v>
+        <v>-31.498</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-3.82</v>
@@ -1712,25 +1712,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.923453</v>
+        <v>-4.874226</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.193573</v>
+        <v>-2.152104</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.807893</v>
+        <v>-1.767941</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.468351</v>
+        <v>-3.428551</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-6.235787</v>
+        <v>-6.019857</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-5.068</v>
+        <v>-4.848</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-30.995</v>
+        <v>-30.992</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-3.422</v>
@@ -1755,25 +1755,25 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-160.4418898921785</v>
+        <v>-158.8377163753962</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-58.49159892870743</v>
+        <v>-57.38582851852524</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-29.12602730501121</v>
+        <v>-28.48238133542684</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-34.65174474559171</v>
+        <v>-34.25410925804315</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-18.41419160177874</v>
+        <v>-17.77655333854555</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-16.27384239933209</v>
+        <v>-15.56740093764049</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-73.78883466254017</v>
+        <v>-73.78169265563623</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>-9.022596039760593</v>
@@ -2520,7 +2520,7 @@
         <v>2.295</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>12.439</v>
+        <v>2.301</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>8.003</v>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -33382,7 +33382,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -35946,7 +35946,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E401" s="5" t="n">
@@ -40128,7 +40128,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">

--- a/output/pdf_financials_xlsx/MDP.xlsx
+++ b/output/pdf_financials_xlsx/MDP.xlsx
@@ -4811,19 +4811,19 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.117079</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.147305</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.051867</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.231162</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>2.581553</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0.477</v>
@@ -18360,7 +18360,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E166" s="5" t="n">
         <v>0.017997</v>
       </c>
@@ -18432,7 +18436,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -19786,7 +19790,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -19862,7 +19870,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -21074,7 +21082,11 @@
           <t>Depreciation of property and equipment 5</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -21150,7 +21162,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -21744,7 +21756,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E211" s="5" t="n">

--- a/output/pdf_financials_xlsx/MDP.xlsx
+++ b/output/pdf_financials_xlsx/MDP.xlsx
@@ -2161,16 +2161,16 @@
         <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.045342</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.145</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.705</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>0</v>
@@ -2204,16 +2204,16 @@
         <v>0.7384540000000001</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.436</v>
+        <v>7.481342</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>14.957</v>
+        <v>15.036</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>18.829</v>
+        <v>18.974</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>14.407</v>
+        <v>15.112</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>22.381</v>
@@ -2505,7 +2505,7 @@
         <v>0.09879499999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.505</v>
+        <v>1.459658</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>1.113</v>
@@ -2861,37 +2861,37 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>0</v>
+        <v>0.157383</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>0.161223</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>0.164668</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>0.173099</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>1.08282</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>1.716</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>1.865</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>2.089</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>1.773</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>1.903</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>2.042</v>
       </c>
       <c r="M56" s="3" t="n">
         <v>0</v>
@@ -2904,34 +2904,34 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>0</v>
+        <v>0.09833799999999999</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>0.121598</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>0.141863</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>0.215708</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>0.617</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>0.868</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>0.874</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>1.125</v>
       </c>
       <c r="L57" s="3" t="n">
         <v>0</v>
@@ -3370,40 +3370,40 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.492338</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.417867</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.64507</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.953837</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>9.500976</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>13.134</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>12.473</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>17.128</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>23.257</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>29.434</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>29.867</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>36.835</v>
       </c>
     </row>
     <row r="68">
@@ -5112,40 +5112,40 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>0.6505030000000001</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.523576</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.320672</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>0.267812</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>0.733927</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>1.475</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>1.883</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>1.216</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>0.469</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>0.411</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="108">
@@ -5499,40 +5499,40 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.85664</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.655287</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.438679</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.719278</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.52957</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-10.637</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-7.617</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.301</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.216</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-2.543</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="117">
@@ -5747,7 +5747,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-1.531</v>
       </c>
     </row>
     <row r="122">
@@ -12236,7 +12236,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -12518,7 +12522,11 @@
           <t>Share-based compensation expense, net 12</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -13382,7 +13390,11 @@
           <t>Purchases of intangible assets 7</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -13662,7 +13674,11 @@
           <t>Repurchase of common shares 11</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -15086,7 +15102,11 @@
           <t>Share-based compensation expense 13</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -15778,7 +15798,11 @@
           <t>Purchases of intangible assets</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E131" s="5" t="n">
         <v>-0.85664</v>
       </c>
@@ -16948,7 +16972,11 @@
           <t>Share-based compensation expense 12</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -18588,7 +18616,11 @@
           <t>Share-based compensation expense 14</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -19946,7 +19978,11 @@
           <t>Share-based compensation expense 11</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -21312,7 +21348,11 @@
           <t>Share-based compensation expense 9</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E205" s="5" t="n">
         <v>0.6505030000000001</v>
       </c>
